--- a/Outputs/PtX_demand_CY.xlsx
+++ b/Outputs/PtX_demand_CY.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K37"/>
+  <dimension ref="A1:K43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,32 +488,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Hydrogen</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>2030</v>
       </c>
       <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="n">
-        <v>4.59950970830188e-05</v>
-      </c>
+      <c r="D2" t="n">
+        <v>0.0002429683964623954</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.0002343469803950105</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="n">
-        <v>6.723258210591231e-10</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1.880690975047868e-05</v>
-      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>Hydrogen</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -522,17 +520,23 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" t="n">
+        <v>4.59950970830188e-05</v>
+      </c>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+      <c r="H3" t="n">
+        <v>6.723258210591231e-10</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.880690975047868e-05</v>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ammonia</t>
+          <t>Methanol</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -551,7 +555,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Synthetic Gases</t>
+          <t>Ammonia</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -570,7 +574,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Biogenic Gases</t>
+          <t>Synthetic Gases</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -579,21 +583,17 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" t="n">
-        <v>1.544500418921626e-05</v>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="n">
-        <v>2.752522045902856e-06</v>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Fossil Gases</t>
+          <t>Biogenic Gases</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -603,12 +603,12 @@
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>0.0001771454336565386</v>
+        <v>1.544500418921626e-05</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>1.295809223857273e-05</v>
+        <v>2.752522045902856e-06</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -616,7 +616,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Synthetic Liquids</t>
+          <t>Fossil Gases</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -625,17 +625,21 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+      <c r="F8" t="n">
+        <v>0.0001771454336565386</v>
+      </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="n">
+        <v>1.295809223857273e-05</v>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Biogenic Liquids</t>
+          <t>Synthetic Liquids</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -644,25 +648,17 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="n">
-        <v>0.000860099140968865</v>
-      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
-      <c r="H9" t="n">
-        <v>0.0018395483296547</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.0006212458405224171</v>
-      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="n">
-        <v>0.001302035356546803</v>
-      </c>
+      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Fossil Liquids</t>
+          <t>Biogenic Liquids</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -672,24 +668,24 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>0.008350637456186499</v>
+        <v>0.000860099140968865</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>0.0168124798601847</v>
+        <v>0.0018395483296547</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0038679851530649</v>
+        <v>0.0006212458405224171</v>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
-        <v>0.01275218025438121</v>
+        <v>0.001302035356546803</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Fossil Liquids</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -697,20 +693,26 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="n">
-        <v>0.0006371951440119037</v>
-      </c>
-      <c r="F11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="n">
+        <v>0.008350637456186499</v>
+      </c>
       <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
+      <c r="H11" t="n">
+        <v>0.0168124798601847</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.0038679851530649</v>
+      </c>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="n">
+        <v>0.01275218025438121</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Renewable Energy Carrier</t>
+          <t>Biomass [Solid]</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -719,7 +721,7 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
-        <v>0.0003052016463952433</v>
+        <v>0.0006371951440119037</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
@@ -731,7 +733,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Overall Demand</t>
+          <t>Fossil Rest</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -740,79 +742,83 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>0.0009423967904071469</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.009449322132084137</v>
-      </c>
+        <v>0.00274681481755719</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
-      <c r="H13" t="n">
-        <v>0.01865202886216522</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.004523748517622271</v>
-      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="n">
-        <v>0.01405421561092801</v>
-      </c>
+      <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Hydrogen</t>
+          <t>Renewable Energy Carrier</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2040</v>
+        <v>2030</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="n">
-        <v>0.0002201371630914197</v>
-      </c>
+      <c r="E14" t="n">
+        <v>0.0003052016463952433</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" t="n">
-        <v>5.62810971135938e-08</v>
-      </c>
-      <c r="I14" t="n">
-        <v>2.630756103747258e-05</v>
-      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>Overall Demand</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2040</v>
+        <v>2030</v>
       </c>
       <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
+      <c r="D15" t="n">
+        <v>0.0002429683964623954</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.003923558588359347</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.009449322132084137</v>
+      </c>
       <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
+      <c r="H15" t="n">
+        <v>0.01865202886216522</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.004523748517622271</v>
+      </c>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="n">
+        <v>0.01405421561092801</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ammonia</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>2040</v>
       </c>
       <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
+      <c r="D16" t="n">
+        <v>0.0003200177929755582</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.0002423267586226396</v>
+      </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
@@ -823,7 +829,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Synthetic Gases</t>
+          <t>Hydrogen</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -833,12 +839,14 @@
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
-        <v>8.204537662679023e-11</v>
+        <v>0.0002201371630914197</v>
       </c>
       <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="H17" t="n">
+        <v>5.62810971135938e-08</v>
+      </c>
       <c r="I17" t="n">
-        <v>7.735919660828944e-12</v>
+        <v>2.630756103747258e-05</v>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
@@ -846,7 +854,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Biogenic Gases</t>
+          <t>Methanol</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -855,21 +863,17 @@
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
-      <c r="F18" t="n">
-        <v>1.863792945036149e-05</v>
-      </c>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
-      <c r="I18" t="n">
-        <v>5.314437067099017e-06</v>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Fossil Gases</t>
+          <t>Ammonia</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -878,21 +882,17 @@
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
-      <c r="F19" t="n">
-        <v>9.714491376137427e-05</v>
-      </c>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" t="n">
-        <v>1.360251149101251e-05</v>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Synthetic Liquids</t>
+          <t>Synthetic Gases</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -901,17 +901,21 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
+      <c r="F20" t="n">
+        <v>8.204537662679023e-11</v>
+      </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="n">
+        <v>7.735919660828944e-12</v>
+      </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Biogenic Liquids</t>
+          <t>Biogenic Gases</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -921,24 +925,20 @@
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="n">
-        <v>0.0003900651332413393</v>
+        <v>1.863792945036149e-05</v>
       </c>
       <c r="G21" t="inlineStr"/>
-      <c r="H21" t="n">
-        <v>0.0022393872034412</v>
-      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
-        <v>0.0004031972244269338</v>
+        <v>5.314437067099017e-06</v>
       </c>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="n">
-        <v>0.001473246606807172</v>
-      </c>
+      <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Fossil Liquids</t>
+          <t>Fossil Gases</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -948,24 +948,20 @@
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="n">
-        <v>0.0023818121080789</v>
+        <v>9.714491376137427e-05</v>
       </c>
       <c r="G22" t="inlineStr"/>
-      <c r="H22" t="n">
-        <v>0.0158510269869034</v>
-      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
-        <v>0.0016958533683974</v>
+        <v>1.360251149101251e-05</v>
       </c>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="n">
-        <v>0.01237113552010564</v>
-      </c>
+      <c r="K22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Synthetic Liquids</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -973,9 +969,7 @@
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="n">
-        <v>0.0005726142571723211</v>
-      </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
@@ -986,7 +980,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Renewable Energy Carrier</t>
+          <t>Biogenic Liquids</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -994,20 +988,26 @@
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" t="n">
-        <v>0.0009991952490496889</v>
-      </c>
-      <c r="F24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="n">
+        <v>0.0003900651332413393</v>
+      </c>
       <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
+      <c r="H24" t="n">
+        <v>0.0022393872034412</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.0004031972244269338</v>
+      </c>
       <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="n">
+        <v>0.001473246606807172</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Overall Demand</t>
+          <t>Fossil Liquids</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1015,61 +1015,57 @@
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" t="n">
-        <v>0.00157180950622201</v>
-      </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="n">
-        <v>0.003107797329668771</v>
+        <v>0.0023818121080789</v>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>0.01809047047144171</v>
+        <v>0.0158510269869034</v>
       </c>
       <c r="I25" t="n">
-        <v>0.002144275110155838</v>
+        <v>0.0016958533683974</v>
       </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="n">
-        <v>0.01384438212691281</v>
+        <v>0.01237113552010564</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Hydrogen</t>
+          <t>Biomass [Solid]</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2050</v>
+        <v>2040</v>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="n">
-        <v>0.0003057668397081666</v>
-      </c>
+      <c r="E26" t="n">
+        <v>0.0005726142571723211</v>
+      </c>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
-      <c r="H26" t="n">
-        <v>9.539192625553469e-08</v>
-      </c>
-      <c r="I26" t="n">
-        <v>4.169633575004193e-05</v>
-      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>Fossil Rest</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2050</v>
+        <v>2040</v>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" t="n">
+        <v>0.001498792873574533</v>
+      </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
@@ -1080,15 +1076,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Ammonia</t>
+          <t>Renewable Energy Carrier</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2050</v>
+        <v>2040</v>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
+      <c r="E28" t="n">
+        <v>0.0009991952490496889</v>
+      </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
@@ -1099,53 +1097,61 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Synthetic Gases</t>
+          <t>Overall Demand</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2050</v>
+        <v>2040</v>
       </c>
       <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
+      <c r="D29" t="n">
+        <v>0.0003200177929755582</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.003312929138419183</v>
+      </c>
       <c r="F29" t="n">
-        <v>8.910218250187293e-10</v>
+        <v>0.003107797329668771</v>
       </c>
       <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+      <c r="H29" t="n">
+        <v>0.01809047047144171</v>
+      </c>
       <c r="I29" t="n">
-        <v>1.587538510713578e-10</v>
+        <v>0.002144275110155838</v>
       </c>
       <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="n">
+        <v>0.01384438212691281</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Biogenic Gases</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>2050</v>
       </c>
       <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="n">
-        <v>3.357789686059986e-06</v>
-      </c>
+      <c r="D30" t="n">
+        <v>0.0003805881714776444</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.0002485998536692391</v>
+      </c>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
-      <c r="I30" t="n">
-        <v>1.568626888927853e-06</v>
-      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Fossil Gases</t>
+          <t>Hydrogen</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1155,12 +1161,14 @@
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="n">
-        <v>6.729120707691278e-06</v>
+        <v>0.0003057668397081666</v>
       </c>
       <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+      <c r="H31" t="n">
+        <v>9.539192625553469e-08</v>
+      </c>
       <c r="I31" t="n">
-        <v>5.294760342702713e-06</v>
+        <v>4.169633575004193e-05</v>
       </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
@@ -1168,7 +1176,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Synthetic Liquids</t>
+          <t>Methanol</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -1177,25 +1185,17 @@
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
-      <c r="F32" t="n">
-        <v>3.262989523006435e-12</v>
-      </c>
+      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
-      <c r="H32" t="n">
-        <v>8.62775039789545e-11</v>
-      </c>
-      <c r="I32" t="n">
-        <v>6.966879730170634e-12</v>
-      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
-      <c r="K32" t="n">
-        <v>1.008722098966015e-10</v>
-      </c>
+      <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Biogenic Liquids</t>
+          <t>Ammonia</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1204,25 +1204,17 @@
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="n">
-        <v>5.017413726574574e-05</v>
-      </c>
+      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
-      <c r="H33" t="n">
-        <v>0.0029331147543705</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0.000103362374024858</v>
-      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
-      <c r="K33" t="n">
-        <v>0.002098804903889274</v>
-      </c>
+      <c r="K33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Fossil Liquids</t>
+          <t>Synthetic Gases</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -1232,24 +1224,20 @@
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="n">
-        <v>0.000203533811730638</v>
+        <v>8.910218250187293e-10</v>
       </c>
       <c r="G34" t="inlineStr"/>
-      <c r="H34" t="n">
-        <v>0.0143748408573499</v>
-      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
-        <v>0.000306157425434054</v>
+        <v>1.587538510713578e-10</v>
       </c>
       <c r="J34" t="inlineStr"/>
-      <c r="K34" t="n">
-        <v>0.01153293881819397</v>
-      </c>
+      <c r="K34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Biogenic Gases</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1257,20 +1245,22 @@
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
-      <c r="E35" t="n">
-        <v>0.0005096977133942317</v>
-      </c>
-      <c r="F35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="n">
+        <v>3.357789686059986e-06</v>
+      </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="n">
+        <v>1.568626888927853e-06</v>
+      </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Renewable Energy Carrier</t>
+          <t>Fossil Gases</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -1278,20 +1268,22 @@
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" t="n">
-        <v>0.00207384498837211</v>
-      </c>
-      <c r="F36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="n">
+        <v>6.729120707691278e-06</v>
+      </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
+      <c r="I36" t="n">
+        <v>5.294760342702713e-06</v>
+      </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Overall Demand</t>
+          <t>Synthetic Liquids</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1299,21 +1291,165 @@
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" t="n">
-        <v>0.002583542701766342</v>
-      </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="n">
-        <v>0.0005695625933831161</v>
+        <v>3.262989523006435e-12</v>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
-        <v>0.01730805108992416</v>
+        <v>8.62775039789545e-11</v>
       </c>
       <c r="I37" t="n">
-        <v>0.0004580796881613153</v>
+        <v>6.966879730170634e-12</v>
       </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="n">
+        <v>1.008722098966015e-10</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Biogenic Liquids</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="n">
+        <v>5.017413726574574e-05</v>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="n">
+        <v>0.0029331147543705</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.000103362374024858</v>
+      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="n">
+        <v>0.002098804903889274</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Fossil Liquids</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="n">
+        <v>0.000203533811730638</v>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="n">
+        <v>0.0143748408573499</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.000306157425434054</v>
+      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="n">
+        <v>0.01153293881819397</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Biomass [Solid]</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="n">
+        <v>0.0005096977133942317</v>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Fossil Rest</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Renewable Energy Carrier</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="n">
+        <v>0.00207384498837211</v>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Overall Demand</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="n">
+        <v>0.0003805881714776444</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.002832142555435581</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.0005695625933831161</v>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="n">
+        <v>0.01730805108992416</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.0004580796881613153</v>
+      </c>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="n">
         <v>0.01363174382295546</v>
       </c>
     </row>

--- a/Outputs/PtX_demand_CY.xlsx
+++ b/Outputs/PtX_demand_CY.xlsx
@@ -501,10 +501,14 @@
       <c r="E2" t="n">
         <v>0.0002343469803950105</v>
       </c>
-      <c r="F2" t="inlineStr"/>
+      <c r="F2" t="n">
+        <v>0.0009961587849847155</v>
+      </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="n">
+        <v>0.0002792631330837626</v>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
     </row>
@@ -712,7 +716,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Fossil Residuals</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -721,7 +725,7 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
-        <v>0.0006371951440119037</v>
+        <v>0.00274681481755719</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
@@ -733,7 +737,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Fossil Rest</t>
+          <t>Biomass [Solid]</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -742,7 +746,7 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>0.00274681481755719</v>
+        <v>0.0006371951440119037</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
@@ -789,14 +793,14 @@
         <v>0.003923558588359347</v>
       </c>
       <c r="F15" t="n">
-        <v>0.009449322132084137</v>
+        <v>0.01044548091706885</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>0.01865202886216522</v>
       </c>
       <c r="I15" t="n">
-        <v>0.004523748517622271</v>
+        <v>0.004803011650706034</v>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="n">
@@ -819,10 +823,14 @@
       <c r="E16" t="n">
         <v>0.0002423267586226396</v>
       </c>
-      <c r="F16" t="inlineStr"/>
+      <c r="F16" t="n">
+        <v>0.002842481773607564</v>
+      </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="n">
+        <v>0.0009051863283643</v>
+      </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
     </row>
@@ -1034,7 +1042,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Fossil Residuals</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1043,7 +1051,7 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="n">
-        <v>0.0005726142571723211</v>
+        <v>0.001498792873574533</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
@@ -1055,7 +1063,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Fossil Rest</t>
+          <t>Biomass [Solid]</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1064,7 +1072,7 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="n">
-        <v>0.001498792873574533</v>
+        <v>0.0005726142571723211</v>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
@@ -1111,14 +1119,14 @@
         <v>0.003312929138419183</v>
       </c>
       <c r="F29" t="n">
-        <v>0.003107797329668771</v>
+        <v>0.005950279103276335</v>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
         <v>0.01809047047144171</v>
       </c>
       <c r="I29" t="n">
-        <v>0.002144275110155838</v>
+        <v>0.003049461438520138</v>
       </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="n">
@@ -1141,10 +1149,14 @@
       <c r="E30" t="n">
         <v>0.0002485998536692391</v>
       </c>
-      <c r="F30" t="inlineStr"/>
+      <c r="F30" t="n">
+        <v>0.003325072504390661</v>
+      </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="n">
+        <v>0.001302704332209</v>
+      </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
     </row>
@@ -1364,7 +1376,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Fossil Residuals</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -1372,9 +1384,7 @@
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" t="n">
-        <v>0.0005096977133942317</v>
-      </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
@@ -1385,7 +1395,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Fossil Rest</t>
+          <t>Biomass [Solid]</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -1393,7 +1403,9 @@
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
+      <c r="E41" t="n">
+        <v>0.0005096977133942317</v>
+      </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
@@ -1439,14 +1451,14 @@
         <v>0.002832142555435581</v>
       </c>
       <c r="F43" t="n">
-        <v>0.0005695625933831161</v>
+        <v>0.003894635097773777</v>
       </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
         <v>0.01730805108992416</v>
       </c>
       <c r="I43" t="n">
-        <v>0.0004580796881613153</v>
+        <v>0.001760784020370315</v>
       </c>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="n">
